--- a/for_client/Samasz_8.xlsx_quotation.xlsx
+++ b/for_client/Samasz_8.xlsx_quotation.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1 530,00 PLN</t>
+          <t>1530,00</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1 500,00 PLN</t>
+          <t>1500,00</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3 230,00 PLN</t>
+          <t>3230,00</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7 210,00 PLN</t>
+          <t>7210,00</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8 060,00 PLN</t>
+          <t>8060,00</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2 060,00 PLN</t>
+          <t>2060,00</t>
         </is>
       </c>
     </row>
